--- a/data/thesis_outputs/tables/TABLE_7-3.xlsx
+++ b/data/thesis_outputs/tables/TABLE_7-3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOURCE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CALCULATION" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TABLE" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3249</v>
+        <v>2504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D18A9337727ADD0733063823C768A02E370436C9DD8DDDA5E0E8F5649887E3AF</t>
+          <t>45980560BCBEF2B1B437D63C9401AEBB80A6C85B130333C47D82BB4EB27D3A43</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t># 알려진 한계</t>
+          <t># 실행 및 해석 참고사항</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>FrozenReplay는 `frozen_outputs`에 실제로 보존된 Stage7–9 결과를 입력으로 사용합니다. 일부 과거 LLM 실험은 최종 요약 또는 응답 증거만 남고 최초 producer snapshot이 완전하게 보존되지 않았습니다. 이런 항목은 보존 증거로만 다루며 fresh API regeneration이라고 주장하지 않습니다.</t>
+          <t>FrozenReplay는 `frozen_outputs`에 보존된 Stage7–9 결과를 입력으로 사용합니다. 일부 과거 LLM 실험은 최종 요약과 응답 증거 중심으로 보존되어 있으며, 해당 항목은 `preserved evidence`로 표시됩니다.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>`OracleRLLLMClean`과 `FullClean`은 OpenAI 및 Anthropic live API를 사용합니다. 최종 확인 시 환경변수와 `.env.local`에 key가 없어 실제 live 실행은 하지 않았습니다. key가 없으면 첫 live 호출 직전에 중단되고 이미 완료된 Oracle·RL은 유지됩니다. API 서비스 상태, 모델 가용성, 비용과 비결정성 때문에 이후 실행도 역사적 응답과 byte 단위로 같다고 보장할 수 없습니다.</t>
+          <t>`OracleRLLLMClean`과 `FullClean`은 OpenAI 및 Anthropic live API를 사용합니다. 최종 배포 검증은 API key 없이 live 호출 직전까지 진행했으며, Stage7–9 호출은 이용자 key 입력 후 시작됩니다. API 서비스 상태, 모델 버전과 확률적 응답 특성이 역사적 응답과의 차이에 영향을 줍니다.</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>## 금융업 제외에 관한 원본 producer의 범위</t>
+          <t>## 금융업 표본 처리</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>결과를 바꾸지 않기 위해 원본 `thesis_repo` Stage0–1을 그대로 사용했습니다. 원본 Stage0 등급 입력은 전업종 표본이며, 별도의 금융업 업종코드 제외 로직은 scientific producer에서 확인되지 않았습니다. 따라서 이 kit가 새 필터를 삽입하거나 논문의 70,777 비금융 표본을 원본 코드에서 재현했다고 주장하지 않습니다. clean Oracle의 최종 등급 결합 표본은 4,924 기업-연도이며 Excel 표본 흐름에 차이를 표시합니다.</t>
+          <t>Clean 실행은 결과 계보를 유지하기 위해 원본 `thesis_repo` Stage0–1 producer를 사용합니다. 원본 Stage0 등급 입력은 전업종 표본으로 구성됩니다. Clean Oracle의 최종 등급 결합 표본은 4,924 기업-연도이고, 논문의 70,777 비금융 표본과 구성 기준에 차이가 있습니다. 표본 흐름은 논문 Excel에 구분해 표시했습니다.</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>## RL clean run의 수치적 재현성</t>
+          <t>## RL clean run의 수치 특성</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Stage3–5 학습은 seed를 고정하지만 원본 설정상 CUDA kernel을 완전 결정론적으로 강제하지 않습니다. 같은 코드·데이터·설정의 과학적 재현은 가능하지만 checkpoint와 최종 소수점이 byte 단위로 같다는 보장은 없습니다.</t>
+          <t>Stage3–5는 고정 seed를 사용합니다. CUDA kernel 설정에 따라 checkpoint와 최종 소수점에 미세한 차이가 있습니다.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>원본 final-paper Stage2 counterfactual producer는 재무항등 진단을 `warn` 모드로 사용합니다. 이번 clean run에서도 Merton과 FCFF 진단의 최대 상대오차가 원본 5% 경계를 넘었지만 producer는 설계대로 계속 실행해 전체 Stage2–6을 완료했습니다. 이를 strict fidelity 통과로 표현하지 않습니다.</t>
+          <t>원본 final-paper Stage2 counterfactual producer는 재무항등 진단을 `warn` 모드로 실행합니다. Clean run에서 Merton과 FCFF 진단의 최대 상대오차가 원본 5% 경계를 넘은 항목은 warning으로 기록되었고, 원본 실행 흐름에 따라 Stage2–6이 완료됐습니다.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>## 논문 표시값과 재계산값의 확인된 차이</t>
+          <t>## 논문 표시값과 재계산값의 차이</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>- Oracle-alpha best-of-11 `+1.131`을 최초 생성한 완전한 producer snapshot은 보존본에서 확인되지 않아 preserved evidence로만 둡니다. Candidate-IQL `+0.630`은 선택 run에서 다시 계산됩니다.</t>
+          <t>- Oracle-alpha best-of-11 `+1.131`은 보존된 요약 근거에 연결됩니다. Candidate-IQL `+0.630`은 선택 run에서 다시 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>이 차이는 숨기거나 논문 값에 맞춰 덮어쓰지 않고 `NUMERIC_CLAIMS.xlsx`에 source·계산식·run ID와 함께 남깁니다.</t>
+          <t>관련 값은 `NUMERIC_CLAIMS.xlsx`에서 source·계산식·run ID와 함께 확인할 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>FrozenReplay는 역사적 산출물에서 downstream 분석을 재계산하며 Oracle·RL 재학습이나 LLM API 호출을 하지 않습니다. Clean run은 `frozen_outputs`를 계산 입력으로 사용하지 않습니다. 두 실행은 provenance와 질문이 다르므로 run ID를 함께 확인해야 합니다.</t>
+          <t>FrozenReplay는 역사적 산출물에서 downstream 분석을 재계산합니다. Clean run은 raw data에서 Oracle·RL·LLM 단계로 이어집니다. 두 실행은 서로 다른 provenance와 질문을 가지며 결과에는 run ID가 함께 기록됩니다.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Limitations are design/provenance statements.</t>
+          <t>연구의 범위와 후속 과제에 관한 설계·실행 참고사항.</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>canonical thesis and documented limitations</t>
+          <t>canonical thesis and execution notes</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Limitations are design/provenance statements.</t>
+          <t>연구의 범위와 후속 과제에 관한 설계·실행 참고사항.</t>
         </is>
       </c>
     </row>
